--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92776</v>
+        <v>92779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92444</v>
+        <v>92447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136177251</v>
       </c>
       <c r="B10" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136177266</v>
       </c>
       <c r="B11" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>136177256</v>
       </c>
       <c r="B19" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136177265</v>
       </c>
       <c r="B20" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92447</v>
+        <v>92448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136177251</v>
       </c>
       <c r="B10" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136177266</v>
       </c>
       <c r="B11" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>136177256</v>
       </c>
       <c r="B19" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136177265</v>
       </c>
       <c r="B20" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92780</v>
+        <v>92785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92448</v>
+        <v>92453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136177251</v>
       </c>
       <c r="B10" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136177266</v>
       </c>
       <c r="B11" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>136177250</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>136177256</v>
       </c>
       <c r="B19" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136177265</v>
       </c>
       <c r="B20" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136177263</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136177255</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136177257</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136177260</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136177262</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136177264</v>
       </c>
       <c r="B8" t="n">
-        <v>92785</v>
+        <v>92787</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92453</v>
+        <v>92455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136177251</v>
       </c>
       <c r="B10" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136177266</v>
       </c>
       <c r="B11" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>136177256</v>
       </c>
       <c r="B19" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136177265</v>
       </c>
       <c r="B20" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92455</v>
+        <v>92457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92457</v>
+        <v>92459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92460</v>
+        <v>92466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92466</v>
+        <v>92470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13546-2025 artfynd.xlsx
+++ b/artfynd/A 13546-2025 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>136588066</v>
       </c>
       <c r="B9" t="n">
-        <v>92470</v>
+        <v>92472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
